--- a/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
+++ b/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
@@ -5,21 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/VulnEnvLLM/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6616C98E-7948-934B-BE44-B509E3485668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6F7B81-32D1-064B-A317-609E815FFC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-3420" windowWidth="38400" windowHeight="21100" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20020" activeTab="2" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase2RawAnalysis_Services_Clas" sheetId="1" r:id="rId1"/>
     <sheet name="Raw analysis" sheetId="2" r:id="rId2"/>
-    <sheet name="Categories" sheetId="3" r:id="rId3"/>
+    <sheet name="CVEs" sheetId="4" r:id="rId3"/>
+    <sheet name="Categories" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Phase2RawAnalysis_Services_Clas!$A$1:$J$44</definedName>
-    <definedName name="categories" localSheetId="2">Categories!$A$1:$B$16</definedName>
+    <definedName name="categories" localSheetId="3">Categories!$A$1:$B$16</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="215">
   <si>
     <t>category_id</t>
   </si>
@@ -625,9 +626,6 @@
     <t>1. Total</t>
   </si>
   <si>
-    <t>CVE-2017-17405</t>
-  </si>
-  <si>
     <t>1. Add blog image webapp
 2. install specific vulnerable version using gem install</t>
   </si>
@@ -646,9 +644,6 @@
     <t>1. install dependencies
 2. install python
 3. configure ssh auth setup</t>
-  </si>
-  <si>
-    <t>CVE-2018-15473</t>
   </si>
   <si>
     <t>1. Repository has not Release file. The Dockerfile used Ubuntu 18.04 and the `bionic-pgdg` repository path no longer provides the required release metadata
@@ -1613,7 +1608,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870DA215-43A6-3F43-AE22-6CE6200E9739}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1637,31 +1631,31 @@
         <v>160</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1684,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -1693,7 +1687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1716,7 +1710,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -1725,7 +1719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1748,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -1757,7 +1751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1780,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -1806,13 +1800,13 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
@@ -1844,7 +1838,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I7" t="s">
         <v>38</v>
@@ -1853,7 +1847,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1876,7 +1870,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I8" t="s">
         <v>44</v>
@@ -1908,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -1931,16 +1925,16 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I10" t="s">
         <v>53</v>
@@ -1963,16 +1957,16 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I11" t="s">
         <v>53</v>
@@ -1998,13 +1992,13 @@
         <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I12" t="s">
         <v>57</v>
@@ -2013,7 +2007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -2036,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I13" t="s">
         <v>60</v>
@@ -2045,7 +2039,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -2068,7 +2062,7 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I14" t="s">
         <v>65</v>
@@ -2077,7 +2071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -2100,7 +2094,7 @@
         <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I15" t="s">
         <v>72</v>
@@ -2109,7 +2103,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2132,7 +2126,7 @@
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I16" t="s">
         <v>75</v>
@@ -2141,7 +2135,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -2164,7 +2158,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I17" t="s">
         <v>80</v>
@@ -2196,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I18" t="s">
         <v>83</v>
@@ -2228,7 +2222,7 @@
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I19" t="s">
         <v>88</v>
@@ -2237,7 +2231,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -2260,7 +2254,7 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I20" t="s">
         <v>92</v>
@@ -2292,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I21" t="s">
         <v>95</v>
@@ -2301,7 +2295,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I22" t="s">
         <v>98</v>
@@ -2333,7 +2327,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -2356,7 +2350,7 @@
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I23" t="s">
         <v>102</v>
@@ -2388,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I24" t="s">
         <v>107</v>
@@ -2397,7 +2391,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -2420,7 +2414,7 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I25" t="s">
         <v>102</v>
@@ -2452,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I26" t="s">
         <v>95</v>
@@ -2461,7 +2455,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>110</v>
       </c>
@@ -2484,7 +2478,7 @@
         <v>71</v>
       </c>
       <c r="H27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I27" t="s">
         <v>112</v>
@@ -2493,7 +2487,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>110</v>
       </c>
@@ -2516,7 +2510,7 @@
         <v>71</v>
       </c>
       <c r="H28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I28" t="s">
         <v>115</v>
@@ -2525,7 +2519,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2548,7 +2542,7 @@
         <v>71</v>
       </c>
       <c r="H29" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I29" t="s">
         <v>118</v>
@@ -2557,7 +2551,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -2580,7 +2574,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I30" t="s">
         <v>123</v>
@@ -2589,7 +2583,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>110</v>
       </c>
@@ -2612,7 +2606,7 @@
         <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I31" t="s">
         <v>112</v>
@@ -2621,7 +2615,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>110</v>
       </c>
@@ -2644,7 +2638,7 @@
         <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I32" t="s">
         <v>115</v>
@@ -2653,7 +2647,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -2676,7 +2670,7 @@
         <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I33" t="s">
         <v>118</v>
@@ -2685,7 +2679,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -2708,7 +2702,7 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I34" t="s">
         <v>123</v>
@@ -2717,7 +2711,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -2740,7 +2734,7 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I35" t="s">
         <v>129</v>
@@ -2749,7 +2743,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>125</v>
       </c>
@@ -2772,7 +2766,7 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I36" t="s">
         <v>129</v>
@@ -2781,7 +2775,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="H37" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I37" t="s">
         <v>134</v>
@@ -2813,7 +2807,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>125</v>
       </c>
@@ -2836,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
@@ -2845,7 +2839,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>139</v>
       </c>
@@ -2868,7 +2862,7 @@
         <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I39" t="s">
         <v>141</v>
@@ -2900,7 +2894,7 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I40" t="s">
         <v>144</v>
@@ -2909,7 +2903,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2932,7 +2926,7 @@
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I41" t="s">
         <v>147</v>
@@ -2941,7 +2935,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>139</v>
       </c>
@@ -2964,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
         <v>150</v>
@@ -2973,7 +2967,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>152</v>
       </c>
@@ -2996,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
         <v>154</v>
@@ -3005,7 +2999,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>152</v>
       </c>
@@ -3028,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I44" t="s">
         <v>157</v>
@@ -3038,17 +3032,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J44" xr:uid="{870DA215-43A6-3F43-AE22-6CE6200E9739}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="E1"/>
-        <filter val="E2"/>
-        <filter val="E3"/>
-        <filter val="E4"/>
-        <filter val="E5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J44" xr:uid="{870DA215-43A6-3F43-AE22-6CE6200E9739}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -3056,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA5F21EE-D000-034A-8890-1F44165791FF}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -3209,7 +3193,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -3428,9 +3412,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -3439,15 +3423,24 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="80" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
@@ -3456,21 +3449,30 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="180" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3478,25 +3480,22 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="G18" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" t="s">
-        <v>104</v>
+      <c r="F18" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="80" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -3504,19 +3503,16 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="G19" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" t="s">
-        <v>109</v>
+      <c r="F19" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -3531,77 +3527,113 @@
         <v>0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>189</v>
+      <c r="H21" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="360" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" t="s">
+        <v>143</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="240" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>153</v>
+      </c>
+      <c r="I24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
@@ -3615,109 +3647,11 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="360" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H26" t="s">
-        <v>143</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="240" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>146</v>
-      </c>
-      <c r="H27" t="s">
-        <v>149</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="H25" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>153</v>
-      </c>
-      <c r="I28" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>152</v>
-      </c>
-      <c r="B29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="H29" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3727,6 +3661,85 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4F5558-3E3C-6F4F-9E2A-41AAF9ADC49A}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23088D9B-5470-0B42-8A75-B767BE835BEE}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -3831,7 +3844,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3860,10 +3873,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
+++ b/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6F7B81-32D1-064B-A317-609E815FFC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D85109-E7EA-724C-B7BC-37DC01E933BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20020" activeTab="2" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="3" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase2RawAnalysis_Services_Clas" sheetId="1" r:id="rId1"/>
@@ -683,9 +683,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>R5</t>
-  </si>
-  <si>
     <t>Missing multi-service orchestration</t>
   </si>
   <si>
@@ -726,6 +723,9 @@
   </si>
   <si>
     <t>E6</t>
+  </si>
+  <si>
+    <t>R4</t>
   </si>
 </sst>
 </file>
@@ -1631,28 +1631,28 @@
         <v>160</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1678,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -1710,7 +1710,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I4" t="s">
         <v>21</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -1800,13 +1800,13 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
@@ -1838,7 +1838,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I7" t="s">
         <v>38</v>
@@ -1870,7 +1870,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I8" t="s">
         <v>44</v>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -1925,16 +1925,16 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I10" t="s">
         <v>53</v>
@@ -1957,16 +1957,16 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I11" t="s">
         <v>53</v>
@@ -1992,13 +1992,13 @@
         <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I12" t="s">
         <v>57</v>
@@ -2030,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I13" t="s">
         <v>60</v>
@@ -2062,7 +2062,7 @@
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I14" t="s">
         <v>65</v>
@@ -2094,7 +2094,7 @@
         <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I15" t="s">
         <v>72</v>
@@ -2126,7 +2126,7 @@
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I16" t="s">
         <v>75</v>
@@ -2158,7 +2158,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I17" t="s">
         <v>80</v>
@@ -2190,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I18" t="s">
         <v>83</v>
@@ -2222,7 +2222,7 @@
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I19" t="s">
         <v>88</v>
@@ -2254,7 +2254,7 @@
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I20" t="s">
         <v>92</v>
@@ -2286,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I21" t="s">
         <v>95</v>
@@ -2318,7 +2318,7 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I22" t="s">
         <v>98</v>
@@ -2350,7 +2350,7 @@
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I23" t="s">
         <v>102</v>
@@ -2382,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I24" t="s">
         <v>107</v>
@@ -2414,7 +2414,7 @@
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I25" t="s">
         <v>102</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I26" t="s">
         <v>95</v>
@@ -2478,7 +2478,7 @@
         <v>71</v>
       </c>
       <c r="H27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I27" t="s">
         <v>112</v>
@@ -2510,7 +2510,7 @@
         <v>71</v>
       </c>
       <c r="H28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I28" t="s">
         <v>115</v>
@@ -2542,7 +2542,7 @@
         <v>71</v>
       </c>
       <c r="H29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I29" t="s">
         <v>118</v>
@@ -2574,7 +2574,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I30" t="s">
         <v>123</v>
@@ -2606,7 +2606,7 @@
         <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I31" t="s">
         <v>112</v>
@@ -2638,7 +2638,7 @@
         <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I32" t="s">
         <v>115</v>
@@ -2670,7 +2670,7 @@
         <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I33" t="s">
         <v>118</v>
@@ -2702,7 +2702,7 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I34" t="s">
         <v>123</v>
@@ -2734,7 +2734,7 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I35" t="s">
         <v>129</v>
@@ -2766,7 +2766,7 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
         <v>129</v>
@@ -2798,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="H37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I37" t="s">
         <v>134</v>
@@ -2830,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I38" t="s">
         <v>137</v>
@@ -2862,7 +2862,7 @@
         <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I39" t="s">
         <v>141</v>
@@ -2894,7 +2894,7 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I40" t="s">
         <v>144</v>
@@ -2926,7 +2926,7 @@
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I41" t="s">
         <v>147</v>
@@ -2958,7 +2958,7 @@
         <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I42" t="s">
         <v>150</v>
@@ -2990,7 +2990,7 @@
         <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I43" t="s">
         <v>154</v>
@@ -3022,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I44" t="s">
         <v>157</v>
@@ -3510,7 +3510,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -3873,10 +3873,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" t="s">
         <v>200</v>
-      </c>
-      <c r="B16" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
+++ b/Analysis/Phase2RawAnalysis_Services_Classified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gx1/Git/Unina/LLM-Generation-Intentionally-Vulnerable-Dockerfiles/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D85109-E7EA-724C-B7BC-37DC01E933BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FBF159-2B08-A947-A812-6BFA4F2AFB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" activeTab="3" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
+    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{39B8D863-7036-364F-B39C-2794CF85470E}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase2RawAnalysis_Services_Clas" sheetId="1" r:id="rId1"/>
@@ -3141,9 +3141,9 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>110</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>110</v>
       </c>
